--- a/prisma/sample-data/work-plan-import-2026-2030-with-errors.xlsx
+++ b/prisma/sample-data/work-plan-import-2026-2030-with-errors.xlsx
@@ -96,223 +96,223 @@
     <t>WL-0219</t>
   </si>
   <si>
+    <t>Spot Repair</t>
+  </si>
+  <si>
+    <t>CIP-2026-005 · condition 55</t>
+  </si>
+  <si>
+    <t>WL-0090</t>
+  </si>
+  <si>
+    <t>Lining</t>
+  </si>
+  <si>
+    <t>CIP-2026-006 · condition 55</t>
+  </si>
+  <si>
+    <t>WL-0252</t>
+  </si>
+  <si>
+    <t>CIP-2027-001 · condition 5</t>
+  </si>
+  <si>
+    <t>WL-0229</t>
+  </si>
+  <si>
+    <t>CIP-2027-002 · condition 6</t>
+  </si>
+  <si>
+    <t>WL-0132</t>
+  </si>
+  <si>
+    <t>CIP-2027-003 · condition 37</t>
+  </si>
+  <si>
+    <t>WL-0258</t>
+  </si>
+  <si>
+    <t>CIP-2027-004 · condition 38</t>
+  </si>
+  <si>
+    <t>WL-0200</t>
+  </si>
+  <si>
+    <t>CIP-2027-005 · condition 56</t>
+  </si>
+  <si>
+    <t>WL-0045</t>
+  </si>
+  <si>
+    <t>CIP-2027-006 · condition 56</t>
+  </si>
+  <si>
+    <t>WL-0026</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>CIP-2028-001 · condition 7</t>
+  </si>
+  <si>
+    <t>WL-0190</t>
+  </si>
+  <si>
+    <t>CIP-2028-002 · condition 7</t>
+  </si>
+  <si>
+    <t>WL-0193</t>
+  </si>
+  <si>
+    <t>CIP-2028-003 · condition 38</t>
+  </si>
+  <si>
+    <t>WL-0067</t>
+  </si>
+  <si>
+    <t>CIP-2028-004 · condition 55</t>
+  </si>
+  <si>
+    <t>WL-0166</t>
+  </si>
+  <si>
+    <t>CIP-2028-005 · condition 56</t>
+  </si>
+  <si>
+    <t>WL-0137</t>
+  </si>
+  <si>
+    <t>CIP-2028-006 · condition 56</t>
+  </si>
+  <si>
+    <t>WL-0227</t>
+  </si>
+  <si>
+    <t>CIP-2029-001 · condition 8</t>
+  </si>
+  <si>
+    <t>WL-0064</t>
+  </si>
+  <si>
+    <t>CIP-2029-002 · condition 8</t>
+  </si>
+  <si>
+    <t>WL-0107</t>
+  </si>
+  <si>
+    <t>CIP-2029-003 · condition 38</t>
+  </si>
+  <si>
+    <t>WL-0247</t>
+  </si>
+  <si>
+    <t>CIP-2029-004 · condition 38</t>
+  </si>
+  <si>
+    <t>WL-0127</t>
+  </si>
+  <si>
+    <t>CIP-2029-005 · condition 57</t>
+  </si>
+  <si>
+    <t>WL-0145</t>
+  </si>
+  <si>
+    <t>CIP-2029-006 · condition 57</t>
+  </si>
+  <si>
+    <t>WL-0098</t>
+  </si>
+  <si>
+    <t>CIP-2030-001 · condition 8</t>
+  </si>
+  <si>
+    <t>WL-0164</t>
+  </si>
+  <si>
+    <t>CIP-2030-002 · condition 9</t>
+  </si>
+  <si>
+    <t>WL-0076</t>
+  </si>
+  <si>
+    <t>CIP-2030-003 · condition 55</t>
+  </si>
+  <si>
+    <t>WL-0062</t>
+  </si>
+  <si>
+    <t>CIP-2030-004 · condition 39</t>
+  </si>
+  <si>
+    <t>WL-0099</t>
+  </si>
+  <si>
+    <t>CIP-2030-005 · condition 57</t>
+  </si>
+  <si>
+    <t>WL-0250</t>
+  </si>
+  <si>
+    <t>CIP-2030-006 · condition 57</t>
+  </si>
+  <si>
+    <t>WL-9999</t>
+  </si>
+  <si>
+    <t>Mistake: no such segment</t>
+  </si>
+  <si>
+    <t>Pipe Bursting</t>
+  </si>
+  <si>
+    <t>Mistake: not in the treatment library</t>
+  </si>
+  <si>
+    <t>Mistake: outside a 2026–2030 plan</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Mistake: cost is not an amount</t>
+  </si>
+  <si>
+    <t>Mistake: programmed after the year it is paid for</t>
+  </si>
+  <si>
+    <t>How to fill in each column</t>
+  </si>
+  <si>
+    <t>Every row is checked before anything is imported, and nothing is written while any row has an error.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>What to put</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>The segment's asset ID. It must be an active segment.</t>
+  </si>
+  <si>
+    <t>WL-0058</t>
+  </si>
+  <si>
+    <t>A treatment or a treatment combination, spelled as in the library (see the Treatments sheet). A combination imports as one project. Anything not in the library must be created in Settings first.</t>
+  </si>
+  <si>
     <t>Dig-once repair</t>
-  </si>
-  <si>
-    <t>CIP-2026-005 · condition 55</t>
-  </si>
-  <si>
-    <t>WL-0090</t>
-  </si>
-  <si>
-    <t>Lining</t>
-  </si>
-  <si>
-    <t>CIP-2026-006 · condition 55</t>
-  </si>
-  <si>
-    <t>WL-0252</t>
-  </si>
-  <si>
-    <t>CIP-2027-001 · condition 5</t>
-  </si>
-  <si>
-    <t>WL-0229</t>
-  </si>
-  <si>
-    <t>CIP-2027-002 · condition 6</t>
-  </si>
-  <si>
-    <t>WL-0132</t>
-  </si>
-  <si>
-    <t>CIP-2027-003 · condition 37</t>
-  </si>
-  <si>
-    <t>WL-0258</t>
-  </si>
-  <si>
-    <t>CIP-2027-004 · condition 38</t>
-  </si>
-  <si>
-    <t>WL-0200</t>
-  </si>
-  <si>
-    <t>CIP-2027-005 · condition 56</t>
-  </si>
-  <si>
-    <t>WL-0045</t>
-  </si>
-  <si>
-    <t>CIP-2027-006 · condition 56</t>
-  </si>
-  <si>
-    <t>WL-0026</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>CIP-2028-001 · condition 7</t>
-  </si>
-  <si>
-    <t>WL-0190</t>
-  </si>
-  <si>
-    <t>CIP-2028-002 · condition 7</t>
-  </si>
-  <si>
-    <t>WL-0193</t>
-  </si>
-  <si>
-    <t>CIP-2028-003 · condition 38</t>
-  </si>
-  <si>
-    <t>WL-0206</t>
-  </si>
-  <si>
-    <t>CIP-2028-004 · condition 38</t>
-  </si>
-  <si>
-    <t>WL-0166</t>
-  </si>
-  <si>
-    <t>CIP-2028-005 · condition 56</t>
-  </si>
-  <si>
-    <t>WL-0137</t>
-  </si>
-  <si>
-    <t>CIP-2028-006 · condition 56</t>
-  </si>
-  <si>
-    <t>WL-0227</t>
-  </si>
-  <si>
-    <t>CIP-2029-001 · condition 8</t>
-  </si>
-  <si>
-    <t>WL-0064</t>
-  </si>
-  <si>
-    <t>CIP-2029-002 · condition 8</t>
-  </si>
-  <si>
-    <t>WL-0107</t>
-  </si>
-  <si>
-    <t>CIP-2029-003 · condition 38</t>
-  </si>
-  <si>
-    <t>WL-0247</t>
-  </si>
-  <si>
-    <t>CIP-2029-004 · condition 38</t>
-  </si>
-  <si>
-    <t>WL-0127</t>
-  </si>
-  <si>
-    <t>Spot Repair</t>
-  </si>
-  <si>
-    <t>CIP-2029-005 · condition 57</t>
-  </si>
-  <si>
-    <t>WL-0145</t>
-  </si>
-  <si>
-    <t>CIP-2029-006 · condition 57</t>
-  </si>
-  <si>
-    <t>WL-0098</t>
-  </si>
-  <si>
-    <t>CIP-2030-001 · condition 8</t>
-  </si>
-  <si>
-    <t>WL-0164</t>
-  </si>
-  <si>
-    <t>CIP-2030-002 · condition 9</t>
-  </si>
-  <si>
-    <t>WL-0253</t>
-  </si>
-  <si>
-    <t>CIP-2030-003 · condition 39</t>
-  </si>
-  <si>
-    <t>WL-0062</t>
-  </si>
-  <si>
-    <t>CIP-2030-004 · condition 39</t>
-  </si>
-  <si>
-    <t>WL-0099</t>
-  </si>
-  <si>
-    <t>CIP-2030-005 · condition 57</t>
-  </si>
-  <si>
-    <t>WL-0250</t>
-  </si>
-  <si>
-    <t>CIP-2030-006 · condition 57</t>
-  </si>
-  <si>
-    <t>WL-9999</t>
-  </si>
-  <si>
-    <t>Mistake: no such segment</t>
-  </si>
-  <si>
-    <t>Pipe Bursting</t>
-  </si>
-  <si>
-    <t>Mistake: not in the treatment library</t>
-  </si>
-  <si>
-    <t>Mistake: outside a 2026–2030 plan</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Mistake: cost is not an amount</t>
-  </si>
-  <si>
-    <t>Mistake: programmed after the year it is paid for</t>
-  </si>
-  <si>
-    <t>How to fill in each column</t>
-  </si>
-  <si>
-    <t>Every row is checked before anything is imported, and nothing is written while any row has an error.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>What to put</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>The segment's asset ID. It must be an active segment.</t>
-  </si>
-  <si>
-    <t>WL-0058</t>
-  </si>
-  <si>
-    <t>A treatment or a treatment combination, spelled as in the library (see the Treatments sheet). A combination imports as one project. Anything not in the library must be created in Settings first.</t>
   </si>
   <si>
     <t>The year the money is spent. It must fall inside the plan. Without the two columns below, it is also the year the work is decided and built.</t>
@@ -1020,7 +1020,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1326,7 +1326,7 @@
         <v>2028</v>
       </c>
       <c r="F21" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G21" t="s">
         <v>45</v>
@@ -1474,7 +1474,7 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>2029</v>
@@ -1487,12 +1487,12 @@
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
@@ -1508,12 +1508,12 @@
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -1537,12 +1537,12 @@
         <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -1564,12 +1564,12 @@
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
         <v>21</v>
@@ -1591,12 +1591,12 @@
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
         <v>21</v>
@@ -1618,12 +1618,12 @@
         <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
         <v>30</v>
@@ -1641,12 +1641,12 @@
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
@@ -1662,22 +1662,22 @@
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C35">
         <v>2027</v>
       </c>
       <c r="F35" s="1"/>
       <c r="I35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1685,14 +1685,14 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>2028</v>
       </c>
       <c r="F36" s="1"/>
       <c r="I36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1700,14 +1700,14 @@
         <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C37">
         <v>2034</v>
       </c>
       <c r="F37" s="1"/>
       <c r="I37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1715,16 +1715,16 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C38">
         <v>2029</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" t="s">
         <v>87</v>
-      </c>
-      <c r="I38" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F39" s="1"/>
       <c r="I39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1769,7 +1769,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1785,16 +1785,16 @@
     </row>
     <row r="4" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1802,13 +1802,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
         <v>96</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,13 +1816,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
         <v>99</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,7 +1830,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
         <v>100</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
         <v>134</v>
